--- a/event_registration_forms/049_modeling_agency_appointment_form--event_registration_forms.xlsx
+++ b/event_registration_forms/049_modeling_agency_appointment_form--event_registration_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -865,12 +865,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>agency</t>
+          <t>agency_2</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Agency</t>
+          <t>Agency 2</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -888,12 +888,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>name_2</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Name</t>
+          <t>Name 2</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -911,12 +911,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>purpose</t>
+          <t>purpose_2</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Purpose</t>
+          <t>Purpose 2</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -1187,12 +1187,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>submit</t>
+          <t>submit_2</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Submit</t>
+          <t>Submit 2</t>
         </is>
       </c>
       <c r="D33" t="inlineStr"/>
@@ -1217,8 +1217,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
-    <col width="46" customWidth="1" min="2" max="2"/>
-    <col width="46" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1241,170 +1241,170 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>agency_choices</t>
+          <t>agency_2_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'value':_'agency_a',_'label':_'agency_a'}</t>
+          <t>agency_a</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'value': 'Agency A', 'label': 'Agency A'}</t>
+          <t>Agency A</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>agency_choices</t>
+          <t>agency_2_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'value':_'agency_b',_'label':_'agency_b'}</t>
+          <t>agency_b</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'value': 'Agency B', 'label': 'Agency B'}</t>
+          <t>Agency B</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>agency_choices</t>
+          <t>agency_2_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'value':_'agency_c',_'label':_'agency_c'}</t>
+          <t>agency_c</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'value': 'Agency C', 'label': 'Agency C'}</t>
+          <t>Agency C</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>name_choices</t>
+          <t>name_2_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'value':_'name_1',_'label':_'name_1'}</t>
+          <t>name_1</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'value': 'Name 1', 'label': 'Name 1'}</t>
+          <t>Name 1</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>name_choices</t>
+          <t>name_2_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'value':_'name_2',_'label':_'name_2'}</t>
+          <t>name_2</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'value': 'Name 2', 'label': 'Name 2'}</t>
+          <t>Name 2</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>name_choices</t>
+          <t>name_2_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'value':_'name_3',_'label':_'name_3'}</t>
+          <t>name_3</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'value': 'Name 3', 'label': 'Name 3'}</t>
+          <t>Name 3</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>name_choices</t>
+          <t>name_2_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'value':_'name_4',_'label':_'name_4'}</t>
+          <t>name_4</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'value': 'Name 4', 'label': 'Name 4'}</t>
+          <t>Name 4</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>purpose_choices</t>
+          <t>purpose_2_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'value':_'purpose_1',_'label':_'purpose_1'}</t>
+          <t>purpose_1</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'value': 'Purpose 1', 'label': 'Purpose 1'}</t>
+          <t>Purpose 1</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>purpose_choices</t>
+          <t>purpose_2_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'value':_'purpose_2',_'label':_'purpose_2'}</t>
+          <t>purpose_2</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'value': 'Purpose 2', 'label': 'Purpose 2'}</t>
+          <t>Purpose 2</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>purpose_choices</t>
+          <t>purpose_2_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'value':_'purpose_3',_'label':_'purpose_3'}</t>
+          <t>purpose_3</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'value': 'Purpose 3', 'label': 'Purpose 3'}</t>
+          <t>Purpose 3</t>
         </is>
       </c>
     </row>
@@ -1416,12 +1416,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'value':_'agency_1',_'label':_'agency_1'}</t>
+          <t>agency_1</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'value': 'Agency 1', 'label': 'Agency 1'}</t>
+          <t>Agency 1</t>
         </is>
       </c>
     </row>
@@ -1433,12 +1433,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'value':_'agency_2',_'label':_'agency_2'}</t>
+          <t>agency_2</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'value': 'Agency 2', 'label': 'Agency 2'}</t>
+          <t>Agency 2</t>
         </is>
       </c>
     </row>
@@ -1450,12 +1450,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'value':_'agency_3',_'label':_'agency_3'}</t>
+          <t>agency_3</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'value': 'Agency 3', 'label': 'Agency 3'}</t>
+          <t>Agency 3</t>
         </is>
       </c>
     </row>
